--- a/docs/shiqiao-waybill-sync-api/STP-狮桥运单同步请求字段-V0.1.xlsx
+++ b/docs/shiqiao-waybill-sync-api/STP-狮桥运单同步请求字段-V0.1.xlsx
@@ -4,18 +4,18 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="24460"/>
+    <workbookView windowWidth="27660" windowHeight="11480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="请求字段" sheetId="1" r:id="rId1"/>
     <sheet name="测试JSON" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">请求字段!$A$4:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">请求字段!$A$4:$D$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">请求字段!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">请求字段!$A$1:$D$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">请求字段!$A$1:$D$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">测试JSON!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">测试JSON!$A$1:$B$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">测试JSON!$A$1:$B$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,12 +35,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="141">
   <si>
     <t>请求字段定义</t>
   </si>
   <si>
-    <t>出发地字段未单独传值时根据提车地点默认回填；deliveryArea 按省市区填写；市编码及新增出发地字段示例暂留空。</t>
+    <t>出发地默认信息由 STP 根据 CRM 的存放地点取值推送；deliveryArea、startArea 使用“省|市|区/县”格式；新增出发地字段示例暂留空。</t>
   </si>
   <si>
     <t>分类</t>
@@ -67,6 +67,15 @@
     <t>CRM20261028VIN01</t>
   </si>
   <si>
+    <t>taskNo</t>
+  </si>
+  <si>
+    <t>STP 任务单号；STP 受理后生成，规则 FY+yyyyMMdd+4 位序列</t>
+  </si>
+  <si>
+    <t>FY202610280001</t>
+  </si>
+  <si>
     <t>customerName</t>
   </si>
   <si>
@@ -109,10 +118,19 @@
     <t>deliveryArea</t>
   </si>
   <si>
-    <t>目的地详细交付地区，按省、市、区填写</t>
-  </si>
-  <si>
-    <t>上海市上海市浦东新区</t>
+    <t>目的地详细交付地区，格式：省|市|区/县；使用英文竖线分隔，固定 3 段，各段去除首尾空格</t>
+  </si>
+  <si>
+    <t>上海市|上海市|浦东新区</t>
+  </si>
+  <si>
+    <t>planPickupDate</t>
+  </si>
+  <si>
+    <t>客户计划提车日期</t>
+  </si>
+  <si>
+    <t>CRM推送计划到达时间</t>
   </si>
   <si>
     <t>deliveryCityCode</t>
@@ -199,31 +217,31 @@
     <t>startContact</t>
   </si>
   <si>
-    <t>出发地联系人；未单独指定时默认取提车地点联系人，当前示例留空</t>
+    <t>出发地联系人；STP 根据 CRM 的存放地点取默认值推送，当前示例留空</t>
   </si>
   <si>
     <t>startPhone</t>
   </si>
   <si>
-    <t>出发地联系电话；未单独指定时默认取提车地点联系电话，当前示例留空</t>
+    <t>出发地联系电话；STP 根据 CRM 的存放地点取默认值推送，当前示例留空</t>
   </si>
   <si>
     <t>startArea</t>
   </si>
   <si>
-    <t>出发地省市区；未单独指定时默认根据提车地点回填，当前示例留空</t>
+    <t>出发地省市区，格式：省|市|区/县；STP 根据 CRM 的存放地点取默认值推送，当前示例留空</t>
   </si>
   <si>
     <t>startCityCode</t>
   </si>
   <si>
-    <t>出发地城市编码；编码规则待确认，当前示例留空</t>
+    <t>出发地城市编码；STP 根据 CRM 的存放地点取默认值推送，编码规则待确认，当前示例留空</t>
   </si>
   <si>
     <t>startAddress</t>
   </si>
   <si>
-    <t>出发地详细地址；未单独指定时默认取提车地点地址，当前示例留空</t>
+    <t>出发地详细地址；STP 根据 CRM 的存放地点取默认值推送，当前示例留空</t>
   </si>
   <si>
     <t>startLongitude</t>
@@ -346,6 +364,9 @@
     <t xml:space="preserve">  "applyNo": "CRM20261028VIN01",</t>
   </si>
   <si>
+    <t xml:space="preserve">  "taskNo": "FY202610280001",</t>
+  </si>
+  <si>
     <t xml:space="preserve">  "customerName": "跨单重复VIN测试客户",</t>
   </si>
   <si>
@@ -358,7 +379,7 @@
     <t xml:space="preserve">  "salesPhone": "13800138000",</t>
   </si>
   <si>
-    <t xml:space="preserve">  "deliveryArea": "上海市上海市浦东新区",</t>
+    <t xml:space="preserve">  "deliveryArea": "上海市|上海市|浦东新区",</t>
   </si>
   <si>
     <t xml:space="preserve">  "deliveryCityCode": "",</t>
@@ -373,6 +394,9 @@
     <t xml:space="preserve">  "receiverPhone": "13800138001",</t>
   </si>
   <si>
+    <t xml:space="preserve">  "planPickupDate": "2026-10-30",</t>
+  </si>
+  <si>
     <t xml:space="preserve">  "endLongitude": 121.5447,</t>
   </si>
   <si>
@@ -412,37 +436,25 @@
     <t xml:space="preserve">  "remark": "跨申请单同 VIN 测试",</t>
   </si>
   <si>
-    <t xml:space="preserve">  "vehicles": [</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "vin": "LSYFZC8B0P000911",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "orderNo": "SO-CROSS-VIN-01",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "vehicleModel": "测试车型",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "engineConfig": "2.0T",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "cabinType": "标准驾驶室",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "mileage": 1200,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "planFreight": 3500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ]</t>
+    <t xml:space="preserve">  "vin": "LSYFZC8B0P000911",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "orderNo": "SO-CROSS-VIN-01",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "vehicleModel": "测试车型",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "engineConfig": "2.0T",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "cabinType": "标准驾驶室",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "mileage": 1200,</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "planFreight": 3500</t>
   </si>
   <si>
     <t>}</t>
@@ -458,7 +470,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,13 +509,6 @@
       <color rgb="FF182230"/>
       <name val="Consolas"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -650,7 +655,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -678,6 +683,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -992,152 +1003,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1154,23 +1165,29 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1520,13 +1537,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="64" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="84" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="62" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:4">
@@ -1534,41 +1554,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1" spans="1:4">
-      <c r="A2" s="8" t="s">
+    <row r="2" ht="28" customHeight="1" spans="1:4">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:4">
-      <c r="A4" s="9" t="s">
+    <row r="4" ht="26" customHeight="1" spans="1:4">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1" spans="1:4">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1" spans="1:4">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -1582,21 +1602,21 @@
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:4">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:4">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -1610,378 +1630,405 @@
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:4">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1" spans="1:4">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="11" t="s">
+    </row>
+    <row r="11" ht="40" customHeight="1" spans="1:4">
+      <c r="A11" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" ht="40" customHeight="1" spans="1:4">
-      <c r="A11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="10"/>
+      <c r="D11" s="13" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="12" ht="40" customHeight="1" spans="1:4">
-      <c r="A12" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="A12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="C12" s="13" t="s">
         <v>30</v>
       </c>
+      <c r="D12" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:4">
-      <c r="A13" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="A13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="C13" s="13" t="s">
         <v>33</v>
       </c>
+      <c r="D13" s="13"/>
     </row>
     <row r="14" ht="40" customHeight="1" spans="1:4">
-      <c r="A14" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:4">
       <c r="A15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1" spans="1:4">
-      <c r="A16" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1" spans="1:4">
       <c r="A17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="C17" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="10" t="s">
+    </row>
+    <row r="18" ht="40" customHeight="1" spans="1:4">
+      <c r="A18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="18" ht="40" customHeight="1" spans="1:4">
-      <c r="A18" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="11" t="s">
+      <c r="C18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1" spans="1:4">
       <c r="A19" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1" spans="1:4">
-      <c r="A20" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="11" t="s">
+      <c r="A20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="11"/>
+      <c r="D20" s="9" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="21" ht="40" customHeight="1" spans="1:4">
       <c r="A21" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="10"/>
+      <c r="C21" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="22" ht="40" customHeight="1" spans="1:4">
-      <c r="A22" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="11"/>
+      <c r="A22" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="13"/>
     </row>
     <row r="23" ht="40" customHeight="1" spans="1:4">
-      <c r="A23" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="10"/>
+      <c r="A23" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="13"/>
     </row>
     <row r="24" ht="40" customHeight="1" spans="1:4">
-      <c r="A24" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="11"/>
+      <c r="A24" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="13"/>
     </row>
     <row r="25" ht="40" customHeight="1" spans="1:4">
-      <c r="A25" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="A25" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>65</v>
       </c>
+      <c r="C25" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="13"/>
     </row>
     <row r="26" ht="40" customHeight="1" spans="1:4">
-      <c r="A26" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="11" t="s">
+      <c r="A26" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="C26" s="13" t="s">
         <v>68</v>
       </c>
+      <c r="D26" s="13"/>
     </row>
     <row r="27" ht="40" customHeight="1" spans="1:4">
       <c r="A27" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="11" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1" spans="1:4">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="C28" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="D28" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1" spans="1:4">
       <c r="A29" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="D29" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="10" t="s">
+    </row>
+    <row r="30" ht="40" customHeight="1" spans="1:4">
+      <c r="A30" s="8" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="30" ht="40" customHeight="1" spans="1:4">
-      <c r="A30" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1" spans="1:4">
       <c r="A31" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="11" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1" spans="1:4">
-      <c r="A32" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="11" t="s">
+      <c r="A32" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1" spans="1:4">
       <c r="A33" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="11" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1" spans="1:4">
-      <c r="A34" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" s="11" t="s">
+      <c r="A34" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1" spans="1:4">
       <c r="A35" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="11" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="36" ht="40" customHeight="1"/>
-    <row r="37" ht="40" customHeight="1"/>
+    <row r="36" ht="40" customHeight="1" spans="1:4">
+      <c r="A36" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1" spans="1:4">
+      <c r="A37" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="38" ht="40" customHeight="1"/>
     <row r="39" ht="40" customHeight="1"/>
     <row r="40" ht="40" customHeight="1"/>
+    <row r="41" ht="40" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:D35" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:D37" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="2">
@@ -2002,7 +2049,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2011,20 +2058,20 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:2">
@@ -2032,15 +2079,15 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1" spans="1:2">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>102</v>
+      <c r="B6" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:2">
@@ -2048,15 +2095,15 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:2">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>104</v>
+      <c r="B8" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:2">
@@ -2064,15 +2111,15 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:2">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>106</v>
+      <c r="B10" s="6" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:2">
@@ -2080,15 +2127,15 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:2">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>108</v>
+      <c r="B12" s="6" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:2">
@@ -2096,15 +2143,15 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:2">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>110</v>
+      <c r="B14" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:2">
@@ -2112,207 +2159,189 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:2">
-      <c r="A16" s="6">
+      <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>112</v>
+      <c r="B16" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:2">
-      <c r="A17" s="4">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:2">
+      <c r="A18" s="4">
         <v>13</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1" spans="1:2">
-      <c r="A18" s="6">
-        <v>14</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>114</v>
+      <c r="B18" s="5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:2">
       <c r="A19" s="4">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:2">
+      <c r="A20" s="4">
         <v>15</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" ht="19" customHeight="1" spans="1:2">
-      <c r="A20" s="6">
-        <v>16</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>116</v>
+      <c r="B20" s="5" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:2">
       <c r="A21" s="4">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="1:2">
+      <c r="A22" s="4">
         <v>17</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="22" ht="19" customHeight="1" spans="1:2">
-      <c r="A22" s="6">
-        <v>18</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>118</v>
+      <c r="B22" s="5" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1" spans="1:2">
       <c r="A23" s="4">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1" spans="1:2">
+      <c r="A24" s="4">
         <v>19</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1" spans="1:2">
-      <c r="A24" s="6">
-        <v>20</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>120</v>
+      <c r="B24" s="5" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1" spans="1:2">
       <c r="A25" s="4">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1" spans="1:2">
+      <c r="A26" s="4">
         <v>21</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="26" ht="19" customHeight="1" spans="1:2">
-      <c r="A26" s="6">
-        <v>22</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>122</v>
+      <c r="B26" s="5" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1" spans="1:2">
       <c r="A27" s="4">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1" spans="1:2">
+      <c r="A28" s="4">
         <v>23</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" ht="19" customHeight="1" spans="1:2">
-      <c r="A28" s="6">
-        <v>24</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>124</v>
+      <c r="B28" s="5" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1" spans="1:2">
       <c r="A29" s="4">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1" spans="1:2">
+      <c r="A30" s="4">
         <v>25</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" ht="19" customHeight="1" spans="1:2">
-      <c r="A30" s="6">
-        <v>26</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>126</v>
+      <c r="B30" s="5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1" spans="1:2">
       <c r="A31" s="4">
+        <v>26</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1" spans="1:2">
+      <c r="A32" s="4">
         <v>27</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" ht="19" customHeight="1" spans="1:2">
-      <c r="A32" s="6">
-        <v>28</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>128</v>
+      <c r="B32" s="5" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1" spans="1:2">
       <c r="A33" s="4">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1" spans="1:2">
+      <c r="A34" s="4">
         <v>29</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="34" ht="19" customHeight="1" spans="1:2">
-      <c r="A34" s="6">
-        <v>30</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>130</v>
+      <c r="B34" s="5" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1" spans="1:2">
       <c r="A35" s="4">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1" spans="1:2">
+      <c r="A36" s="4">
         <v>31</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" ht="19" customHeight="1" spans="1:2">
-      <c r="A36" s="6">
-        <v>32</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>132</v>
+      <c r="B36" s="5" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1" spans="1:2">
       <c r="A37" s="4">
+        <v>32</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1" spans="1:2">
+      <c r="A38" s="4">
         <v>33</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="38" ht="19" customHeight="1" spans="1:2">
-      <c r="A38" s="6">
-        <v>34</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="39" ht="19" customHeight="1" spans="1:2">
-      <c r="A39" s="4">
-        <v>35</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" ht="19" customHeight="1" spans="1:2">
-      <c r="A40" s="6">
-        <v>36</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>136</v>
+      <c r="B38" s="5" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
